--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/49.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/49.xlsx
@@ -426,13 +426,13 @@
         <v>-14.12459899240203</v>
       </c>
       <c r="E2">
-        <v>-13.70401767995965</v>
+        <v>-15.20833158786917</v>
       </c>
       <c r="F2">
-        <v>3.267490931258128</v>
+        <v>3.147266656620225</v>
       </c>
       <c r="G2">
-        <v>-17.97192531059117</v>
+        <v>-16.48929259490401</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.86545774908328</v>
       </c>
       <c r="E3">
-        <v>-14.79969712561929</v>
+        <v>-14.71394992460688</v>
       </c>
       <c r="F3">
-        <v>3.562310203384083</v>
+        <v>3.172979180803121</v>
       </c>
       <c r="G3">
-        <v>-16.95095839318434</v>
+        <v>-16.52975260920478</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.5189882179585</v>
       </c>
       <c r="E4">
-        <v>-13.67386951895272</v>
+        <v>-16.19942901915831</v>
       </c>
       <c r="F4">
-        <v>3.728810394611978</v>
+        <v>3.024704729171621</v>
       </c>
       <c r="G4">
-        <v>-17.54894030417277</v>
+        <v>-16.42748713282629</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.11390232602039</v>
       </c>
       <c r="E5">
-        <v>-15.82752555786521</v>
+        <v>-16.81634287613701</v>
       </c>
       <c r="F5">
-        <v>3.661851800708889</v>
+        <v>3.377426882753262</v>
       </c>
       <c r="G5">
-        <v>-15.84857279495905</v>
+        <v>-15.84222085336888</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.64465267053538</v>
       </c>
       <c r="E6">
-        <v>-16.69896481767471</v>
+        <v>-17.02403666806904</v>
       </c>
       <c r="F6">
-        <v>3.587017089539982</v>
+        <v>3.612742867601323</v>
       </c>
       <c r="G6">
-        <v>-16.03357537817453</v>
+        <v>-15.63722779881925</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.12832505929214</v>
       </c>
       <c r="E7">
-        <v>-18.47413870855557</v>
+        <v>-17.48158765330275</v>
       </c>
       <c r="F7">
-        <v>4.404655477738427</v>
+        <v>3.726686460591201</v>
       </c>
       <c r="G7">
-        <v>-16.44090505465232</v>
+        <v>-15.26515361729986</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.5639743640513</v>
       </c>
       <c r="E8">
-        <v>-16.51182942180058</v>
+        <v>-18.39493696859109</v>
       </c>
       <c r="F8">
-        <v>3.891210167196016</v>
+        <v>4.245274275970192</v>
       </c>
       <c r="G8">
-        <v>-15.74485835533249</v>
+        <v>-15.44466188852333</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.95899007040667</v>
       </c>
       <c r="E9">
-        <v>-18.08333813573451</v>
+        <v>-19.31645149734405</v>
       </c>
       <c r="F9">
-        <v>4.619832194289628</v>
+        <v>4.330640850298292</v>
       </c>
       <c r="G9">
-        <v>-15.47016364168932</v>
+        <v>-14.21397385811237</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.31844840902342</v>
       </c>
       <c r="E10">
-        <v>-18.17153573142857</v>
+        <v>-19.78553179721548</v>
       </c>
       <c r="F10">
-        <v>5.396100257657461</v>
+        <v>4.549376233211918</v>
       </c>
       <c r="G10">
-        <v>-14.40743786454763</v>
+        <v>-14.45242360459711</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.647414669885459</v>
       </c>
       <c r="E11">
-        <v>-20.18572693405331</v>
+        <v>-19.17430368654047</v>
       </c>
       <c r="F11">
-        <v>5.076297424663073</v>
+        <v>4.871102535315607</v>
       </c>
       <c r="G11">
-        <v>-14.78301566530831</v>
+        <v>-14.0673374720356</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.961493236991769</v>
       </c>
       <c r="E12">
-        <v>-19.8947487954245</v>
+        <v>-20.30773166993148</v>
       </c>
       <c r="F12">
-        <v>5.355700779422929</v>
+        <v>4.842646458294638</v>
       </c>
       <c r="G12">
-        <v>-13.81097932302812</v>
+        <v>-13.26889084299083</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.261541926356418</v>
       </c>
       <c r="E13">
-        <v>-21.9659054445806</v>
+        <v>-21.40467784504519</v>
       </c>
       <c r="F13">
-        <v>5.702574659140805</v>
+        <v>5.465335205183444</v>
       </c>
       <c r="G13">
-        <v>-13.39200180955708</v>
+        <v>-13.12117230328105</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.569960546909955</v>
       </c>
       <c r="E14">
-        <v>-20.30851247366055</v>
+        <v>-22.32021590270172</v>
       </c>
       <c r="F14">
-        <v>5.455083330206397</v>
+        <v>5.676481085952621</v>
       </c>
       <c r="G14">
-        <v>-12.778492495113</v>
+        <v>-12.40476571226743</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.8885437159501</v>
       </c>
       <c r="E15">
-        <v>-22.58828077445145</v>
+        <v>-22.10985159588783</v>
       </c>
       <c r="F15">
-        <v>6.364097269872851</v>
+        <v>6.025742320525366</v>
       </c>
       <c r="G15">
-        <v>-12.20446024963115</v>
+        <v>-12.37725238039398</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.231055620602684</v>
       </c>
       <c r="E16">
-        <v>-22.23696893490686</v>
+        <v>-23.77976234574091</v>
       </c>
       <c r="F16">
-        <v>5.629176337048352</v>
+        <v>6.126382333026283</v>
       </c>
       <c r="G16">
-        <v>-11.81164370233536</v>
+        <v>-11.38898242824625</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.599825897552794</v>
       </c>
       <c r="E17">
-        <v>-24.04747419452804</v>
+        <v>-23.89259679101385</v>
       </c>
       <c r="F17">
-        <v>6.923705839038474</v>
+        <v>6.617759935958116</v>
       </c>
       <c r="G17">
-        <v>-11.93130979141363</v>
+        <v>-10.88252277964389</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.998620230237709</v>
       </c>
       <c r="E18">
-        <v>-26.22341636540956</v>
+        <v>-24.94468828381942</v>
       </c>
       <c r="F18">
-        <v>5.83546964157193</v>
+        <v>6.619862332426421</v>
       </c>
       <c r="G18">
-        <v>-10.60843506411816</v>
+        <v>-10.71413236426168</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.433249560773036</v>
       </c>
       <c r="E19">
-        <v>-27.9930000338472</v>
+        <v>-25.56344201341503</v>
       </c>
       <c r="F19">
-        <v>6.963507236008184</v>
+        <v>6.988827114042154</v>
       </c>
       <c r="G19">
-        <v>-10.68734743012915</v>
+        <v>-10.0683072532688</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.901719554410371</v>
       </c>
       <c r="E20">
-        <v>-25.95503584959914</v>
+        <v>-26.86415304254748</v>
       </c>
       <c r="F20">
-        <v>6.775457895163863</v>
+        <v>7.398183090218391</v>
       </c>
       <c r="G20">
-        <v>-10.66492505020837</v>
+        <v>-9.784254325638789</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.416133600505149</v>
       </c>
       <c r="E21">
-        <v>-28.04239417613339</v>
+        <v>-26.7648456065595</v>
       </c>
       <c r="F21">
-        <v>6.776571220953226</v>
+        <v>7.087368043544378</v>
       </c>
       <c r="G21">
-        <v>-10.70059695892905</v>
+        <v>-8.929654496556061</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.976440548003322</v>
       </c>
       <c r="E22">
-        <v>-26.50492102900644</v>
+        <v>-27.4952376565665</v>
       </c>
       <c r="F22">
-        <v>7.48506392015881</v>
+        <v>7.269761291762384</v>
       </c>
       <c r="G22">
-        <v>-10.13124186238218</v>
+        <v>-8.540349400735318</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.596063801011271</v>
       </c>
       <c r="E23">
-        <v>-28.50869805423418</v>
+        <v>-28.03971535482887</v>
       </c>
       <c r="F23">
-        <v>6.992662455117116</v>
+        <v>6.907849230214086</v>
       </c>
       <c r="G23">
-        <v>-9.771780187982451</v>
+        <v>-8.072048395076667</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.283061335242035</v>
       </c>
       <c r="E24">
-        <v>-29.43151669134313</v>
+        <v>-28.12407953647012</v>
       </c>
       <c r="F24">
-        <v>7.512867243666372</v>
+        <v>6.881846777440209</v>
       </c>
       <c r="G24">
-        <v>-7.805012300691532</v>
+        <v>-7.870581151097342</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.047733856591172</v>
       </c>
       <c r="E25">
-        <v>-28.52805409561354</v>
+        <v>-27.9215398797922</v>
       </c>
       <c r="F25">
-        <v>7.259115113901605</v>
+        <v>6.953694395754622</v>
       </c>
       <c r="G25">
-        <v>-7.961720939400811</v>
+        <v>-7.618841409271539</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.897337058319986</v>
       </c>
       <c r="E26">
-        <v>-29.24443321061057</v>
+        <v>-29.21318444860255</v>
       </c>
       <c r="F26">
-        <v>7.548438996677389</v>
+        <v>6.631053576038243</v>
       </c>
       <c r="G26">
-        <v>-7.948625444531787</v>
+        <v>-6.998759545319336</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.830329987637656</v>
       </c>
       <c r="E27">
-        <v>-29.7246461934382</v>
+        <v>-28.8215656931505</v>
       </c>
       <c r="F27">
-        <v>7.323454410077042</v>
+        <v>6.723847292499843</v>
       </c>
       <c r="G27">
-        <v>-8.554089749518347</v>
+        <v>-6.724858498031868</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.844951460647015</v>
       </c>
       <c r="E28">
-        <v>-27.8623067798775</v>
+        <v>-29.08102511103518</v>
       </c>
       <c r="F28">
-        <v>7.235944020910497</v>
+        <v>6.698411443029482</v>
       </c>
       <c r="G28">
-        <v>-7.647700579981706</v>
+        <v>-6.503462135216279</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.930354087936776</v>
       </c>
       <c r="E29">
-        <v>-29.87281408405712</v>
+        <v>-28.62057310769108</v>
       </c>
       <c r="F29">
-        <v>7.461824901040672</v>
+        <v>6.582821055642838</v>
       </c>
       <c r="G29">
-        <v>-8.243493381630486</v>
+        <v>-6.370468195000377</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.076864045645223</v>
       </c>
       <c r="E30">
-        <v>-29.07031190242279</v>
+        <v>-28.91062092698313</v>
       </c>
       <c r="F30">
-        <v>7.423474803760667</v>
+        <v>6.530695208454277</v>
       </c>
       <c r="G30">
-        <v>-7.423371045618</v>
+        <v>-6.14380073885533</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.270756694968846</v>
       </c>
       <c r="E31">
-        <v>-29.4698176061807</v>
+        <v>-29.17557089023925</v>
       </c>
       <c r="F31">
-        <v>6.922559378552999</v>
+        <v>6.525365492584664</v>
       </c>
       <c r="G31">
-        <v>-7.171298433856831</v>
+        <v>-6.221569598735413</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.494508595332081</v>
       </c>
       <c r="E32">
-        <v>-29.25053220144108</v>
+        <v>-27.91434236456627</v>
       </c>
       <c r="F32">
-        <v>6.916769090407431</v>
+        <v>6.196559962656651</v>
       </c>
       <c r="G32">
-        <v>-6.762541985459997</v>
+        <v>-6.393962285575806</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.73394166915439</v>
       </c>
       <c r="E33">
-        <v>-28.23443036137081</v>
+        <v>-29.0857037035926</v>
       </c>
       <c r="F33">
-        <v>6.120588731411103</v>
+        <v>6.384973785158205</v>
       </c>
       <c r="G33">
-        <v>-8.204465360737935</v>
+        <v>-6.310893614175763</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.971889319200314</v>
       </c>
       <c r="E34">
-        <v>-26.35616545898505</v>
+        <v>-28.09663303942999</v>
       </c>
       <c r="F34">
-        <v>6.700487331740897</v>
+        <v>6.242236141247016</v>
       </c>
       <c r="G34">
-        <v>-6.535861475591995</v>
+        <v>-6.662258064226154</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.197301255056217</v>
       </c>
       <c r="E35">
-        <v>-28.85335229602507</v>
+        <v>-27.81539210475223</v>
       </c>
       <c r="F35">
-        <v>6.544297001208244</v>
+        <v>6.516429065043264</v>
       </c>
       <c r="G35">
-        <v>-7.395864240606032</v>
+        <v>-7.056840780237834</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.401676956790773</v>
       </c>
       <c r="E36">
-        <v>-25.56081303064641</v>
+        <v>-26.90552733376542</v>
       </c>
       <c r="F36">
-        <v>6.644446620206705</v>
+        <v>6.885367338902108</v>
       </c>
       <c r="G36">
-        <v>-8.100592971063605</v>
+        <v>-6.753657621616439</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.581379783411388</v>
       </c>
       <c r="E37">
-        <v>-27.21725076296175</v>
+        <v>-26.91580653179437</v>
       </c>
       <c r="F37">
-        <v>6.546715834024419</v>
+        <v>6.584920138641532</v>
       </c>
       <c r="G37">
-        <v>-8.645297417181185</v>
+        <v>-6.882865982175226</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.739680889064215</v>
       </c>
       <c r="E38">
-        <v>-27.63783401419316</v>
+        <v>-26.4233519585868</v>
       </c>
       <c r="F38">
-        <v>6.811546549434227</v>
+        <v>6.728779392016111</v>
       </c>
       <c r="G38">
-        <v>-8.111073805224629</v>
+        <v>-7.760402507863179</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.878381045296978</v>
       </c>
       <c r="E39">
-        <v>-27.71427802183796</v>
+        <v>-26.67372415009277</v>
       </c>
       <c r="F39">
-        <v>7.127903374032969</v>
+        <v>6.77439758488828</v>
       </c>
       <c r="G39">
-        <v>-8.049334917133983</v>
+        <v>-7.847973408310597</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.008213399874673</v>
       </c>
       <c r="E40">
-        <v>-25.81233150847803</v>
+        <v>-25.20144396113165</v>
       </c>
       <c r="F40">
-        <v>6.701123517906247</v>
+        <v>7.048240937640546</v>
       </c>
       <c r="G40">
-        <v>-8.748590221556286</v>
+        <v>-7.666979623414782</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.134253868213255</v>
       </c>
       <c r="E41">
-        <v>-24.89666885448176</v>
+        <v>-25.29351650299177</v>
       </c>
       <c r="F41">
-        <v>6.9588070793647</v>
+        <v>7.021115218668474</v>
       </c>
       <c r="G41">
-        <v>-8.925763181743008</v>
+        <v>-8.166292358698971</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.266340202063472</v>
       </c>
       <c r="E42">
-        <v>-23.68523110277649</v>
+        <v>-25.3745996476864</v>
       </c>
       <c r="F42">
-        <v>7.557080525423393</v>
+        <v>7.242032521321073</v>
       </c>
       <c r="G42">
-        <v>-8.376690959924495</v>
+        <v>-8.919811989447565</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.409620195152414</v>
       </c>
       <c r="E43">
-        <v>-24.08492785425534</v>
+        <v>-24.73829444703207</v>
       </c>
       <c r="F43">
-        <v>7.2642327677161</v>
+        <v>7.30999012631194</v>
       </c>
       <c r="G43">
-        <v>-9.444925408153431</v>
+        <v>-9.079233191787011</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.568638186686923</v>
       </c>
       <c r="E44">
-        <v>-22.78964922553576</v>
+        <v>-23.39805730572122</v>
       </c>
       <c r="F44">
-        <v>7.443874179422007</v>
+        <v>7.764359587156302</v>
       </c>
       <c r="G44">
-        <v>-9.038281052130808</v>
+        <v>-9.122469732960438</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.746743484665811</v>
       </c>
       <c r="E45">
-        <v>-21.90793907411997</v>
+        <v>-23.17276220419457</v>
       </c>
       <c r="F45">
-        <v>7.1392453805121</v>
+        <v>7.29039592376612</v>
       </c>
       <c r="G45">
-        <v>-8.581437299110259</v>
+        <v>-8.795463529945135</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.941696661276843</v>
       </c>
       <c r="E46">
-        <v>-22.15579857277441</v>
+        <v>-22.7222426057338</v>
       </c>
       <c r="F46">
-        <v>6.713908540401055</v>
+        <v>7.795895534180879</v>
       </c>
       <c r="G46">
-        <v>-8.809799128494937</v>
+        <v>-9.237798069900572</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.155836180159243</v>
       </c>
       <c r="E47">
-        <v>-22.36736315766117</v>
+        <v>-22.23282403000468</v>
       </c>
       <c r="F47">
-        <v>7.482428055083101</v>
+        <v>7.645727434666579</v>
       </c>
       <c r="G47">
-        <v>-9.528296925926043</v>
+        <v>-9.098319040120344</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.382229254011332</v>
       </c>
       <c r="E48">
-        <v>-20.42686653678418</v>
+        <v>-21.36027170956012</v>
       </c>
       <c r="F48">
-        <v>6.93538084921353</v>
+        <v>7.503345988738594</v>
       </c>
       <c r="G48">
-        <v>-10.31867765955657</v>
+        <v>-9.177412852880417</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.620995404353277</v>
       </c>
       <c r="E49">
-        <v>-21.53174534552832</v>
+        <v>-20.41565701941847</v>
       </c>
       <c r="F49">
-        <v>7.014885895799421</v>
+        <v>7.698232674125623</v>
       </c>
       <c r="G49">
-        <v>-8.634868797911983</v>
+        <v>-9.128328243822896</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.865470181251861</v>
       </c>
       <c r="E50">
-        <v>-20.25669285596066</v>
+        <v>-20.66787738996398</v>
       </c>
       <c r="F50">
-        <v>7.408642057046138</v>
+        <v>7.633084891365053</v>
       </c>
       <c r="G50">
-        <v>-10.3859735175094</v>
+        <v>-9.829236149571376</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.113437249752808</v>
       </c>
       <c r="E51">
-        <v>-19.68524420335485</v>
+        <v>-20.18279892006931</v>
       </c>
       <c r="F51">
-        <v>6.942035952927622</v>
+        <v>7.900405679187676</v>
       </c>
       <c r="G51">
-        <v>-9.793467643300829</v>
+        <v>-9.100773140035992</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.361343210189061</v>
       </c>
       <c r="E52">
-        <v>-20.35114934112123</v>
+        <v>-19.29387048737096</v>
       </c>
       <c r="F52">
-        <v>7.001905378597553</v>
+        <v>7.648113132786642</v>
       </c>
       <c r="G52">
-        <v>-9.452544866242595</v>
+        <v>-9.723622393254775</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.605996123620867</v>
       </c>
       <c r="E53">
-        <v>-18.32736006712481</v>
+        <v>-19.07352186053218</v>
       </c>
       <c r="F53">
-        <v>6.640967477114947</v>
+        <v>7.578989186492634</v>
       </c>
       <c r="G53">
-        <v>-10.71981073374735</v>
+        <v>-10.06971313923112</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.849338501311396</v>
       </c>
       <c r="E54">
-        <v>-18.27584363385163</v>
+        <v>-19.19496591288149</v>
       </c>
       <c r="F54">
-        <v>7.201071409987444</v>
+        <v>7.6039230453169</v>
       </c>
       <c r="G54">
-        <v>-10.57478126096641</v>
+        <v>-9.465404088726125</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.0855554308161</v>
       </c>
       <c r="E55">
-        <v>-18.37018382909512</v>
+        <v>-18.48372432029328</v>
       </c>
       <c r="F55">
-        <v>6.77575279395926</v>
+        <v>7.502148169474147</v>
       </c>
       <c r="G55">
-        <v>-9.615827359832299</v>
+        <v>-9.950704957789808</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.320340566720599</v>
       </c>
       <c r="E56">
-        <v>-17.63425970160345</v>
+        <v>-18.18814027030523</v>
       </c>
       <c r="F56">
-        <v>7.486283276975731</v>
+        <v>7.444849996222505</v>
       </c>
       <c r="G56">
-        <v>-10.07077832302429</v>
+        <v>-10.04153276211464</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.549654135202741</v>
       </c>
       <c r="E57">
-        <v>-16.97697247733608</v>
+        <v>-17.35793409252863</v>
       </c>
       <c r="F57">
-        <v>6.934824186318849</v>
+        <v>7.404935941286014</v>
       </c>
       <c r="G57">
-        <v>-9.349574488824496</v>
+        <v>-10.33772434672103</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.776356006504911</v>
       </c>
       <c r="E58">
-        <v>-16.44755017012621</v>
+        <v>-17.45032227844944</v>
       </c>
       <c r="F58">
-        <v>7.015295109296404</v>
+        <v>7.662836535004</v>
       </c>
       <c r="G58">
-        <v>-11.90468541807345</v>
+        <v>-10.3508955531832</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.99858268566894</v>
       </c>
       <c r="E59">
-        <v>-17.35359813990551</v>
+        <v>-16.84708494636339</v>
       </c>
       <c r="F59">
-        <v>6.923858258640589</v>
+        <v>7.64049049594608</v>
       </c>
       <c r="G59">
-        <v>-10.97794288370449</v>
+        <v>-10.32196067087989</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.216654797481631</v>
       </c>
       <c r="E60">
-        <v>-17.72427640385778</v>
+        <v>-16.80796169568351</v>
       </c>
       <c r="F60">
-        <v>6.884896826217317</v>
+        <v>7.395873601899386</v>
       </c>
       <c r="G60">
-        <v>-10.90006306717929</v>
+        <v>-10.61426355141782</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.432050741635363</v>
       </c>
       <c r="E61">
-        <v>-17.79137983923303</v>
+        <v>-16.81553715314</v>
       </c>
       <c r="F61">
-        <v>6.911141162272811</v>
+        <v>7.620697485223589</v>
       </c>
       <c r="G61">
-        <v>-10.79783805734195</v>
+        <v>-10.58397499804402</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.641168757252789</v>
       </c>
       <c r="E62">
-        <v>-16.64497722366326</v>
+        <v>-16.21269852934113</v>
       </c>
       <c r="F62">
-        <v>7.000193971543369</v>
+        <v>7.874872082363784</v>
       </c>
       <c r="G62">
-        <v>-11.4669079328018</v>
+        <v>-10.7842504371175</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.848998413915798</v>
       </c>
       <c r="E63">
-        <v>-16.47646898058099</v>
+        <v>-15.8125033925033</v>
       </c>
       <c r="F63">
-        <v>6.697447223372623</v>
+        <v>7.76543315131033</v>
       </c>
       <c r="G63">
-        <v>-11.79820097843572</v>
+        <v>-11.36249381362482</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.050271418099086</v>
       </c>
       <c r="E64">
-        <v>-15.6539587033893</v>
+        <v>-16.16484938166778</v>
       </c>
       <c r="F64">
-        <v>7.067919633661451</v>
+        <v>7.347684156608929</v>
       </c>
       <c r="G64">
-        <v>-11.02852475478502</v>
+        <v>-11.05016521670075</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.248897205208864</v>
       </c>
       <c r="E65">
-        <v>-15.31606588963522</v>
+        <v>-15.97405915982781</v>
       </c>
       <c r="F65">
-        <v>6.983691236144797</v>
+        <v>7.560203470531947</v>
       </c>
       <c r="G65">
-        <v>-10.34374863986503</v>
+        <v>-11.27506258801303</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.44099807718907</v>
       </c>
       <c r="E66">
-        <v>-15.60517923637919</v>
+        <v>-15.76305110525857</v>
       </c>
       <c r="F66">
-        <v>6.675406023518933</v>
+        <v>7.472514154006397</v>
       </c>
       <c r="G66">
-        <v>-11.57022031776134</v>
+        <v>-11.33817733850319</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.628118150262182</v>
       </c>
       <c r="E67">
-        <v>-14.76169939520843</v>
+        <v>-15.42651223839639</v>
       </c>
       <c r="F67">
-        <v>6.768544340820099</v>
+        <v>7.289418450230817</v>
       </c>
       <c r="G67">
-        <v>-12.5648565705945</v>
+        <v>-11.35369038286359</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.808113727543166</v>
       </c>
       <c r="E68">
-        <v>-16.60089919187286</v>
+        <v>-15.67906901905921</v>
       </c>
       <c r="F68">
-        <v>7.031994996136842</v>
+        <v>7.326597236003264</v>
       </c>
       <c r="G68">
-        <v>-11.81496195871066</v>
+        <v>-11.08370023097361</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.979319755986481</v>
       </c>
       <c r="E69">
-        <v>-14.56788148231266</v>
+        <v>-15.32012357709958</v>
       </c>
       <c r="F69">
-        <v>7.159769011283861</v>
+        <v>7.550082477604542</v>
       </c>
       <c r="G69">
-        <v>-11.34658393608658</v>
+        <v>-11.56003580311141</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.14254253836265</v>
       </c>
       <c r="E70">
-        <v>-14.78379447945652</v>
+        <v>-15.40027640245745</v>
       </c>
       <c r="F70">
-        <v>7.085638412407333</v>
+        <v>7.606428028342965</v>
       </c>
       <c r="G70">
-        <v>-11.5360365334576</v>
+        <v>-10.61251957403096</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.28946283081193</v>
       </c>
       <c r="E71">
-        <v>-17.22693350092089</v>
+        <v>-16.16011056754616</v>
       </c>
       <c r="F71">
-        <v>6.747477301032101</v>
+        <v>7.055789021414856</v>
       </c>
       <c r="G71">
-        <v>-11.32766517540707</v>
+        <v>-11.39726501546156</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.42039149648771</v>
       </c>
       <c r="E72">
-        <v>-15.0326798213082</v>
+        <v>-14.65440118063149</v>
       </c>
       <c r="F72">
-        <v>7.243758838988508</v>
+        <v>7.343515811838041</v>
       </c>
       <c r="G72">
-        <v>-11.59394545923308</v>
+        <v>-11.0212734116832</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.52554720792701</v>
       </c>
       <c r="E73">
-        <v>-14.88364598612805</v>
+        <v>-15.3542006760198</v>
       </c>
       <c r="F73">
-        <v>7.403698360386231</v>
+        <v>7.489303504526338</v>
       </c>
       <c r="G73">
-        <v>-11.07396084827646</v>
+        <v>-10.95657002310934</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.60357780594886</v>
       </c>
       <c r="E74">
-        <v>-15.0072538615776</v>
+        <v>-14.60931807170047</v>
       </c>
       <c r="F74">
-        <v>6.190456551632824</v>
+        <v>7.446137279166455</v>
       </c>
       <c r="G74">
-        <v>-10.93940568279507</v>
+        <v>-11.16421298341895</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.64560124783337</v>
       </c>
       <c r="E75">
-        <v>-14.75835606009195</v>
+        <v>-15.55316857095836</v>
       </c>
       <c r="F75">
-        <v>7.464754008176971</v>
+        <v>7.293684542355234</v>
       </c>
       <c r="G75">
-        <v>-10.98638211559527</v>
+        <v>-10.88598332159941</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.6511519614873</v>
       </c>
       <c r="E76">
-        <v>-14.42763584229585</v>
+        <v>-15.74272944224619</v>
       </c>
       <c r="F76">
-        <v>7.196795377454193</v>
+        <v>7.495388691467302</v>
       </c>
       <c r="G76">
-        <v>-10.84805181343513</v>
+        <v>-10.76696469717974</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.61462955271024</v>
       </c>
       <c r="E77">
-        <v>-17.64688546403092</v>
+        <v>-16.18367173539191</v>
       </c>
       <c r="F77">
-        <v>7.132505783322923</v>
+        <v>7.713297363712935</v>
       </c>
       <c r="G77">
-        <v>-11.05319759654333</v>
+        <v>-10.16652477015878</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.53136424231954</v>
       </c>
       <c r="E78">
-        <v>-14.65174727859492</v>
+        <v>-15.59009892605874</v>
       </c>
       <c r="F78">
-        <v>7.356852527023113</v>
+        <v>7.704208516569419</v>
       </c>
       <c r="G78">
-        <v>-10.66653718499339</v>
+        <v>-10.09087844563127</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.39987742992577</v>
       </c>
       <c r="E79">
-        <v>-15.74242210460815</v>
+        <v>-16.82589110897279</v>
       </c>
       <c r="F79">
-        <v>7.008693021096092</v>
+        <v>7.725696366998037</v>
       </c>
       <c r="G79">
-        <v>-10.50920066220994</v>
+        <v>-9.531168744976268</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.21487234279227</v>
       </c>
       <c r="E80">
-        <v>-16.24910557981458</v>
+        <v>-17.88709890063636</v>
       </c>
       <c r="F80">
-        <v>6.745172782917513</v>
+        <v>7.560196843592725</v>
       </c>
       <c r="G80">
-        <v>-9.389503216600984</v>
+        <v>-9.831999622721069</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.977781309968808</v>
       </c>
       <c r="E81">
-        <v>-17.46360840147756</v>
+        <v>-17.47333937561164</v>
       </c>
       <c r="F81">
-        <v>6.761831251387812</v>
+        <v>7.742310103628585</v>
       </c>
       <c r="G81">
-        <v>-9.987453798654318</v>
+        <v>-9.575854249397763</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.683566080179389</v>
       </c>
       <c r="E82">
-        <v>-17.47006664508767</v>
+        <v>-18.5686367258294</v>
       </c>
       <c r="F82">
-        <v>7.156425720446162</v>
+        <v>7.540380638582954</v>
       </c>
       <c r="G82">
-        <v>-8.38475685533874</v>
+        <v>-9.131886688700584</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.339097916447821</v>
       </c>
       <c r="E83">
-        <v>-18.57086284709951</v>
+        <v>-18.86637629249503</v>
       </c>
       <c r="F83">
-        <v>6.912698492990074</v>
+        <v>7.561076569774498</v>
       </c>
       <c r="G83">
-        <v>-9.42992537510519</v>
+        <v>-9.314457363329431</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.943298194922912</v>
       </c>
       <c r="E84">
-        <v>-20.75736663438006</v>
+        <v>-20.05203921471841</v>
       </c>
       <c r="F84">
-        <v>7.513047827760182</v>
+        <v>7.530975355091569</v>
       </c>
       <c r="G84">
-        <v>-8.577568175626229</v>
+        <v>-8.382574272860568</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.507576520998272</v>
       </c>
       <c r="E85">
-        <v>-19.80340721875755</v>
+        <v>-20.61300516194035</v>
       </c>
       <c r="F85">
-        <v>6.817303702883684</v>
+        <v>7.526069763332191</v>
       </c>
       <c r="G85">
-        <v>-9.798575565093341</v>
+        <v>-8.780856413957856</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.040177018324551</v>
       </c>
       <c r="E86">
-        <v>-22.06448606858673</v>
+        <v>-20.97124455797476</v>
       </c>
       <c r="F86">
-        <v>6.322885991583576</v>
+        <v>7.377028243485698</v>
       </c>
       <c r="G86">
-        <v>-9.204903993424841</v>
+        <v>-9.111789176838194</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.554936110448124</v>
       </c>
       <c r="E87">
-        <v>-21.59432593377084</v>
+        <v>-22.87981959660912</v>
       </c>
       <c r="F87">
-        <v>7.191883158755592</v>
+        <v>7.456566424767701</v>
       </c>
       <c r="G87">
-        <v>-8.958838704967823</v>
+        <v>-8.392980700800747</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.069266353151374</v>
       </c>
       <c r="E88">
-        <v>-24.01459322046937</v>
+        <v>-25.02823012961835</v>
       </c>
       <c r="F88">
-        <v>6.416976931397961</v>
+        <v>7.726249716423108</v>
       </c>
       <c r="G88">
-        <v>-8.373618113540754</v>
+        <v>-8.263149677656978</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.596650640728728</v>
       </c>
       <c r="E89">
-        <v>-24.9700934774934</v>
+        <v>-25.37661810839026</v>
       </c>
       <c r="F89">
-        <v>6.509088073119655</v>
+        <v>7.256124707577499</v>
       </c>
       <c r="G89">
-        <v>-8.625840843115913</v>
+        <v>-7.639616409355323</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.157247542355551</v>
       </c>
       <c r="E90">
-        <v>-28.03366827913992</v>
+        <v>-26.70166695588621</v>
       </c>
       <c r="F90">
-        <v>6.410247274617618</v>
+        <v>7.271538968208792</v>
       </c>
       <c r="G90">
-        <v>-6.985408197480383</v>
+        <v>-7.881290425410089</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.756006883354397</v>
       </c>
       <c r="E91">
-        <v>-28.82646232930247</v>
+        <v>-28.88457613876513</v>
       </c>
       <c r="F91">
-        <v>6.790305552491642</v>
+        <v>7.063441479481917</v>
       </c>
       <c r="G91">
-        <v>-8.041604502399696</v>
+        <v>-7.474831432253435</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.406516125192828</v>
       </c>
       <c r="E92">
-        <v>-29.45808478418806</v>
+        <v>-30.54053002196113</v>
       </c>
       <c r="F92">
-        <v>5.971852050768841</v>
+        <v>6.964077152781311</v>
       </c>
       <c r="G92">
-        <v>-7.427266276547942</v>
+        <v>-7.249143005330056</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.105127784871213</v>
       </c>
       <c r="E93">
-        <v>-33.17063623424097</v>
+        <v>-32.28895100209311</v>
       </c>
       <c r="F93">
-        <v>6.402251872445796</v>
+        <v>6.364445184182027</v>
       </c>
       <c r="G93">
-        <v>-7.785049242175584</v>
+        <v>-6.88697790490623</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.848706856489419</v>
       </c>
       <c r="E94">
-        <v>-35.47407576297773</v>
+        <v>-34.61272465347624</v>
       </c>
       <c r="F94">
-        <v>6.030894765770778</v>
+        <v>6.32043402407129</v>
       </c>
       <c r="G94">
-        <v>-7.467868576428936</v>
+        <v>-7.119015662675197</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.626928904161378</v>
       </c>
       <c r="E95">
-        <v>-37.02140032736718</v>
+        <v>-36.4388833665807</v>
       </c>
       <c r="F95">
-        <v>5.440734350055104</v>
+        <v>5.814639514861134</v>
       </c>
       <c r="G95">
-        <v>-7.742200396573938</v>
+        <v>-7.15026105394164</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.421568566962993</v>
       </c>
       <c r="E96">
-        <v>-38.24921211472058</v>
+        <v>-38.49606653623442</v>
       </c>
       <c r="F96">
-        <v>4.953134102480036</v>
+        <v>5.284275628483944</v>
       </c>
       <c r="G96">
-        <v>-7.33625049861255</v>
+        <v>-6.8969457277551</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.222172678631417</v>
       </c>
       <c r="E97">
-        <v>-41.45646103233256</v>
+        <v>-40.62351165847591</v>
       </c>
       <c r="F97">
-        <v>5.567703192086601</v>
+        <v>4.770858482433228</v>
       </c>
       <c r="G97">
-        <v>-7.758676805688453</v>
+        <v>-7.071750742597681</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.000068676825334</v>
       </c>
       <c r="E98">
-        <v>-42.59383456648216</v>
+        <v>-43.74039292747661</v>
       </c>
       <c r="F98">
-        <v>4.827601649524994</v>
+        <v>4.723320133921369</v>
       </c>
       <c r="G98">
-        <v>-7.381852374385526</v>
+        <v>-6.864575105569886</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.756108211153456</v>
       </c>
       <c r="E99">
-        <v>-46.54757338119617</v>
+        <v>-45.61691555771161</v>
       </c>
       <c r="F99">
-        <v>4.163439860247629</v>
+        <v>4.206871163176407</v>
       </c>
       <c r="G99">
-        <v>-7.007683070331761</v>
+        <v>-6.514080033468336</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.457423582962555</v>
       </c>
       <c r="E100">
-        <v>-48.49330512494811</v>
+        <v>-47.89459271660046</v>
       </c>
       <c r="F100">
-        <v>4.10425466605241</v>
+        <v>4.124644101304916</v>
       </c>
       <c r="G100">
-        <v>-7.816964289429649</v>
+        <v>-6.250287789237659</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.128358063536809</v>
       </c>
       <c r="E101">
-        <v>-49.83375096512803</v>
+        <v>-50.15196274871657</v>
       </c>
       <c r="F101">
-        <v>3.44333179331999</v>
+        <v>3.361096447774472</v>
       </c>
       <c r="G101">
-        <v>-6.781589977996759</v>
+        <v>-6.070916582105221</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.720836000573486</v>
       </c>
       <c r="E102">
-        <v>-52.82999701968492</v>
+        <v>-52.69090493411358</v>
       </c>
       <c r="F102">
-        <v>3.238077261519523</v>
+        <v>2.805825210329908</v>
       </c>
       <c r="G102">
-        <v>-6.200393849356893</v>
+        <v>-6.266414358576966</v>
       </c>
     </row>
   </sheetData>
